--- a/Data/AddClientData.xlsx
+++ b/Data/AddClientData.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\POM9PMSept26\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211B891D-7FB6-453E-B88B-C5FFADE55199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C5357D-3002-4417-BA07-A34AB7731ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddClient" sheetId="1" r:id="rId1"/>
+    <sheet name="dbTesting" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
   <si>
     <t>Name</t>
   </si>
@@ -335,6 +336,9 @@
   </si>
   <si>
     <t>//div[contains(@class,'alert')]</t>
+  </si>
+  <si>
+    <t>Nagesh3</t>
   </si>
 </sst>
 </file>
@@ -718,7 +722,7 @@
     <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1078,4 +1082,137 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C415E-3634-41E6-9C14-CE4AA8373917}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/AddClientData.xlsx
+++ b/Data/AddClientData.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\POM9PMSept26\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C5357D-3002-4417-BA07-A34AB7731ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF12B499-9597-4607-98C4-906AA69545D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddClient" sheetId="1" r:id="rId1"/>
     <sheet name="dbTesting" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="109">
   <si>
     <t>Name</t>
   </si>
@@ -339,6 +340,15 @@
   </si>
   <si>
     <t>Nagesh3</t>
+  </si>
+  <si>
+    <t>Data From excel</t>
+  </si>
+  <si>
+    <t>Data from database</t>
+  </si>
+  <si>
+    <t>Nagesh4</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1171,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>
@@ -1209,6 +1219,254 @@
         <v>32</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B8BA83-E256-44C7-82FB-2D9168A022B4}">
+  <dimension ref="A5:Q18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>33</v>
       </c>
     </row>
